--- a/examples/bookings-team/existing/manual_cases.xlsx
+++ b/examples/bookings-team/existing/manual_cases.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -427,6 +427,7 @@
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +466,11 @@
           <t>Criteria</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +508,11 @@
           <t>AC-5</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>refund</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,6 +548,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>AC-5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>refund</t>
         </is>
       </c>
     </row>

--- a/examples/bookings-team/existing/manual_cases.xlsx
+++ b/examples/bookings-team/existing/manual_cases.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -556,6 +556,48 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Refund status after a late cancel</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A booking made two days ago</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1. Cancel the booking 2. Open its refund status</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The status is no_refund and the amount is 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AC-5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>refund</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
